--- a/docs/downloads/04/tbl_cm_write_sex_alaotra_tous.xlsx
+++ b/docs/downloads/04/tbl_cm_write_sex_alaotra_tous.xlsx
@@ -384,7 +384,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -401,7 +401,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -424,7 +424,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -441,7 +441,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -464,7 +464,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -481,7 +481,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -504,7 +504,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -527,7 +527,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -544,7 +544,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -601,7 +601,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -624,7 +624,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -641,7 +641,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -658,7 +658,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -681,7 +681,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -698,7 +698,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -715,7 +715,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -738,7 +738,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -755,7 +755,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -778,7 +778,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -801,7 +801,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -818,7 +818,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -841,7 +841,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -858,7 +858,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -875,7 +875,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -898,7 +898,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -915,7 +915,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -938,7 +938,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -961,7 +961,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -984,7 +984,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1001,7 +1001,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1024,7 +1024,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1041,7 +1041,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1064,7 +1064,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1104,7 +1104,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1127,7 +1127,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1144,7 +1144,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1161,7 +1161,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1184,7 +1184,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1201,7 +1201,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1218,7 +1218,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1241,7 +1241,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1264,7 +1264,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1287,7 +1287,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1310,7 +1310,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1333,7 +1333,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
